--- a/templates/TATA Capital/TATA_Collection_Agency_Template_2026-27.xlsx
+++ b/templates/TATA Capital/TATA_Collection_Agency_Template_2026-27.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-report-generator\templates\TATA Capital\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-automation-final\templates\TATA Capital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A905D2-1C3D-4A90-936C-4CDC777FFD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD3E203-2AFA-4EEE-AED9-A383A0E32CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2652" yWindow="2652" windowWidth="13152" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="2" r:id="rId1"/>
@@ -837,6 +837,15 @@
     <xf numFmtId="15" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -845,15 +854,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1164,7 +1164,7 @@
   <dimension ref="A1:J62"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" style="40" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.44140625" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.44140625" style="25" customWidth="1"/>
@@ -1172,8 +1172,8 @@
     <col min="6" max="6" width="18.5546875" style="25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.5546875" style="25" customWidth="1"/>
     <col min="8" max="8" width="33.6640625" style="25" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" style="43" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" style="44" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" style="41" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="8.6640625" style="25"/>
   </cols>
   <sheetData>
@@ -2427,13 +2427,13 @@
       <c r="J58" s="27"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B60" s="45"/>
+      <c r="B60" s="42"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B61" s="45"/>
+      <c r="B61" s="42"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B62" s="45"/>
+      <c r="B62" s="42"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0"/>
@@ -2452,6 +2452,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2747,13 +2750,13 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="42"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="45"/>
       <c r="F13" s="1" t="str" cm="1">
         <f t="array" ref="F13">_xlfn.IFS(F12&gt;=80%,B16,F12&gt;=70%,B17,F12&gt;=60%,B18,F12&gt;=50%,B19,F12&lt;=49%,B20)</f>
         <v>E</v>
@@ -2877,11 +2880,28 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B89E9B38EF334341B754D8F8D6A719DA" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fa1e129258e112aee4cf2e89d18a6563">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xmlns:ns4="2bc29a05-2ca3-4765-9547-41c11361a102" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5debfbfacc377353d2d2775bb411679" ns3:_="" ns4:_="">
     <xsd:import namespace="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
@@ -3120,24 +3140,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05142686-EBCF-43E0-A14A-D80EE15D7AEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="2bc29a05-2ca3-4765-9547-41c11361a102"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{690F940F-5541-43CF-85B5-16E943A4DE36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC960972-EEAE-4599-9007-3F4FCECAD8D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3154,29 +3182,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{690F940F-5541-43CF-85B5-16E943A4DE36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05142686-EBCF-43E0-A14A-D80EE15D7AEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="2bc29a05-2ca3-4765-9547-41c11361a102"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>